--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,129 +485,129 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,129 +485,129 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,19 +617,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,9 +639,99 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.60</t>
-        </is>
-      </c>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,96 +643,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,6 +643,86 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,205 +448,181 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -656,7 +632,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -666,7 +642,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -676,7 +652,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -686,7 +662,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -696,7 +672,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -706,7 +682,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -716,12 +692,22 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,255 +448,315 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.66</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.93</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -706,7 +766,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -716,12 +776,46 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.68</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>3.50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -695,17 +695,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.68</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,372 +448,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
           <t>3.75</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.66</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.93</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.71</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3.61</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.81</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.09</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.38</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,66 +448,284 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>3.75</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.08</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.78</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.09</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,17 +448,17 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,34 +470,34 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,225 +507,139 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.08</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3.67</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.78</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.09</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,12 +453,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,198 +448,176 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.91</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,174 +448,108 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,110 +448,198 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>4.10</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>3.80</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.80</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.50</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,215 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>3.80</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.50</t>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.25</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,396 +448,110 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.25</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,100 +458,386 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.33</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,149 +448,149 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -602,242 +602,22 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.90</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,78 +448,78 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>3.90</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,29 +529,315 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
@@ -480,12 +480,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3.20</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -634,210 +634,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.75</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,196 +448,86 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2.75</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,61 +448,61 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -514,22 +514,154 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.60</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,122 +448,122 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,95 +573,183 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.73</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,310 +448,290 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>3.70</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
+          <t>WdE2Z2y1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -649,9 +649,21 @@
           <t>lYpTkOLs</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.60</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -659,9 +671,21 @@
           <t>p0vxl2jf</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -669,9 +693,21 @@
           <t>hQspntL6</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -679,9 +715,21 @@
           <t>vaZNtoqR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -689,9 +737,21 @@
           <t>WdE2Z2y1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.20</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -699,9 +759,21 @@
           <t>vNHAXt6D</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -709,9 +781,21 @@
           <t>KdJMr7EE</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -719,9 +803,21 @@
           <t>h2acepbK</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.85</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -729,9 +825,21 @@
           <t>AsQgyP6l</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>10.00</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,24 +463,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -492,352 +492,66 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.54</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.85</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.98</t>
+          <t>1.67</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,73 +485,359 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>3.10</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.95</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -629,213 +629,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
         <is>
           <t>1.95</t>
         </is>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,144 +448,144 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>3.60</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,51 +595,249 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>3.75</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.95</t>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QB1LGiQc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.50</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>12.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
@@ -497,12 +497,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,205 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
           <t>2.05</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>7.50</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>6.50</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,161 +485,161 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/france/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -502,12 +502,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -640,6 +640,94 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.75</t>
         </is>
       </c>
     </row>
